--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/MINNESOTA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/MINNESOTA_2021.xlsx
@@ -841,7 +841,7 @@
         <v>6</v>
       </c>
       <c r="D27">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="28">
@@ -2929,7 +2929,7 @@
         <v>6</v>
       </c>
       <c r="D143">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="144">
@@ -2983,7 +2983,7 @@
         <v>6</v>
       </c>
       <c r="D146">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="147">
@@ -3181,7 +3181,7 @@
         <v>6</v>
       </c>
       <c r="D157">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="158">
@@ -3577,7 +3577,7 @@
         <v>6</v>
       </c>
       <c r="D179">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="180">
@@ -4009,7 +4009,7 @@
         <v>6</v>
       </c>
       <c r="D203">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="204">
@@ -4117,7 +4117,7 @@
         <v>6</v>
       </c>
       <c r="D209">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="210">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C210">
@@ -4153,7 +4153,7 @@
         <v>6</v>
       </c>
       <c r="D211">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="212">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C216">
@@ -4531,7 +4531,7 @@
         <v>6</v>
       </c>
       <c r="D232">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="233">
@@ -4855,7 +4855,7 @@
         <v>6</v>
       </c>
       <c r="D250">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="251">
@@ -5035,7 +5035,7 @@
         <v>6</v>
       </c>
       <c r="D260">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="261">
@@ -6961,7 +6961,7 @@
         <v>6</v>
       </c>
       <c r="D367">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="368">
@@ -7483,7 +7483,7 @@
         <v>6</v>
       </c>
       <c r="D396">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="397">
@@ -7789,7 +7789,7 @@
         <v>6</v>
       </c>
       <c r="D413">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="414">
@@ -8743,7 +8743,7 @@
         <v>6</v>
       </c>
       <c r="D466">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="467">
@@ -9301,7 +9301,7 @@
         <v>6</v>
       </c>
       <c r="D497">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="498">
@@ -9769,7 +9769,7 @@
         <v>6</v>
       </c>
       <c r="D523">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="524">
@@ -10273,7 +10273,7 @@
         <v>6</v>
       </c>
       <c r="D551">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="552">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C586">
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="D588">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="589">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C607">
@@ -11335,7 +11335,7 @@
         <v>6</v>
       </c>
       <c r="D610">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="611">
@@ -12163,7 +12163,7 @@
         <v>6</v>
       </c>
       <c r="D656">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="657">
@@ -12847,7 +12847,7 @@
         <v>6</v>
       </c>
       <c r="D694">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="695">
@@ -13639,7 +13639,7 @@
         <v>6</v>
       </c>
       <c r="D738">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="739">
@@ -15097,7 +15097,7 @@
         <v>6</v>
       </c>
       <c r="D819">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="820">
@@ -16123,7 +16123,7 @@
         <v>6</v>
       </c>
       <c r="D876">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="877">
@@ -16519,7 +16519,7 @@
         <v>6</v>
       </c>
       <c r="D898">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="899">
@@ -17005,7 +17005,7 @@
         <v>6</v>
       </c>
       <c r="D925">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="926">
@@ -17869,7 +17869,7 @@
         <v>6</v>
       </c>
       <c r="D973">
-        <v>0.0009310986964618249</v>
+        <v>0.0009310986964618248</v>
       </c>
     </row>
     <row r="974">
